--- a/Team-Data/2008-09/12-27-2008-09.xlsx
+++ b/Team-Data/2008-09/12-27-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,67 +728,67 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>0.655</v>
+        <v>0.643</v>
       </c>
       <c r="H2" t="n">
         <v>48</v>
       </c>
       <c r="I2" t="n">
-        <v>35.7</v>
+        <v>35.2</v>
       </c>
       <c r="J2" t="n">
-        <v>78.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="K2" t="n">
-        <v>0.455</v>
+        <v>0.451</v>
       </c>
       <c r="L2" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="N2" t="n">
-        <v>0.379</v>
+        <v>0.376</v>
       </c>
       <c r="O2" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P2" t="n">
         <v>23.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.748</v>
+        <v>0.744</v>
       </c>
       <c r="R2" t="n">
         <v>11</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T2" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U2" t="n">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="V2" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="W2" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y2" t="n">
         <v>4.3</v>
@@ -733,34 +800,34 @@
         <v>20.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF2" t="n">
         <v>6</v>
       </c>
       <c r="AG2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH2" t="n">
         <v>26</v>
       </c>
       <c r="AI2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AL2" t="n">
         <v>3</v>
@@ -769,13 +836,13 @@
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AO2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ2" t="n">
         <v>24</v>
@@ -784,25 +851,25 @@
         <v>17</v>
       </c>
       <c r="AS2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT2" t="n">
         <v>18</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="n">
         <v>9</v>
       </c>
       <c r="AW2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX2" t="n">
         <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
@@ -811,10 +878,10 @@
         <v>22</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -843,97 +910,97 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>0.867</v>
+        <v>0.871</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J3" t="n">
         <v>76</v>
       </c>
       <c r="K3" t="n">
-        <v>0.486</v>
+        <v>0.485</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M3" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="N3" t="n">
-        <v>0.375</v>
+        <v>0.37</v>
       </c>
       <c r="O3" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="P3" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.763</v>
+        <v>0.757</v>
       </c>
       <c r="R3" t="n">
         <v>10.8</v>
       </c>
       <c r="S3" t="n">
-        <v>32.4</v>
+        <v>32.2</v>
       </c>
       <c r="T3" t="n">
-        <v>43.3</v>
+        <v>43</v>
       </c>
       <c r="U3" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="V3" t="n">
         <v>16.5</v>
       </c>
       <c r="W3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.7</v>
+        <v>101.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI3" t="n">
         <v>10</v>
@@ -951,7 +1018,7 @@
         <v>22</v>
       </c>
       <c r="AN3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO3" t="n">
         <v>3</v>
@@ -960,19 +1027,19 @@
         <v>3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AR3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU3" t="n">
         <v>6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5</v>
       </c>
       <c r="AV3" t="n">
         <v>30</v>
@@ -981,10 +1048,10 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
         <v>26</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="n">
         <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>0.355</v>
+        <v>0.367</v>
       </c>
       <c r="H4" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="I4" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="J4" t="n">
-        <v>75.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.446</v>
+        <v>0.444</v>
       </c>
       <c r="L4" t="n">
         <v>5.3</v>
@@ -1058,10 +1125,10 @@
         <v>0.362</v>
       </c>
       <c r="O4" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="P4" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q4" t="n">
         <v>0.739</v>
@@ -1073,49 +1140,49 @@
         <v>28.4</v>
       </c>
       <c r="T4" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="U4" t="n">
         <v>19.5</v>
       </c>
       <c r="V4" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W4" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X4" t="n">
         <v>4.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>91.40000000000001</v>
+        <v>91</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.1</v>
+        <v>-1.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE4" t="n">
         <v>21</v>
       </c>
       <c r="AF4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
         <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1127,7 +1194,7 @@
         <v>19</v>
       </c>
       <c r="AL4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM4" t="n">
         <v>25</v>
@@ -1136,10 +1203,10 @@
         <v>16</v>
       </c>
       <c r="AO4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
         <v>28</v>
@@ -1148,31 +1215,31 @@
         <v>20</v>
       </c>
       <c r="AS4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT4" t="n">
         <v>29</v>
       </c>
-      <c r="AT4" t="n">
-        <v>28</v>
-      </c>
       <c r="AU4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX4" t="n">
         <v>20</v>
       </c>
       <c r="AY4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -1210,61 +1277,61 @@
         <v>29</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.414</v>
+        <v>0.448</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
       </c>
       <c r="I5" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
       <c r="J5" t="n">
-        <v>84.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L5" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="M5" t="n">
-        <v>16.4</v>
+        <v>16.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.385</v>
+        <v>0.377</v>
       </c>
       <c r="O5" t="n">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="P5" t="n">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="R5" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="S5" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="T5" t="n">
-        <v>42.1</v>
+        <v>42.5</v>
       </c>
       <c r="U5" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V5" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="W5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="X5" t="n">
         <v>5.5</v>
@@ -1273,25 +1340,25 @@
         <v>5.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>19.7</v>
+        <v>20.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>99.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.4</v>
+        <v>-2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
         <v>18</v>
@@ -1300,67 +1367,67 @@
         <v>5</v>
       </c>
       <c r="AI5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM5" t="n">
         <v>21</v>
       </c>
       <c r="AN5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AP5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AQ5" t="n">
         <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AS5" t="n">
         <v>14</v>
       </c>
       <c r="AT5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV5" t="n">
         <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
         <v>26</v>
       </c>
       <c r="AZ5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
         <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -1389,85 +1456,85 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" t="n">
         <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.893</v>
+        <v>0.862</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>38.3</v>
+        <v>38</v>
       </c>
       <c r="J6" t="n">
-        <v>79.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.481</v>
+        <v>0.479</v>
       </c>
       <c r="L6" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="M6" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.346</v>
+        <v>0.342</v>
       </c>
       <c r="O6" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="P6" t="n">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.778</v>
+        <v>0.776</v>
       </c>
       <c r="R6" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S6" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T6" t="n">
         <v>42.1</v>
       </c>
       <c r="U6" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V6" t="n">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
       <c r="W6" t="n">
         <v>8.1</v>
       </c>
       <c r="X6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>102.6</v>
+        <v>102</v>
       </c>
       <c r="AC6" t="n">
-        <v>13.4</v>
+        <v>12.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1476,7 +1543,7 @@
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>26</v>
@@ -1485,61 +1552,61 @@
         <v>4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK6" t="n">
         <v>3</v>
       </c>
       <c r="AL6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN6" t="n">
         <v>20</v>
       </c>
       <c r="AO6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AV6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX6" t="n">
         <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BA6" t="n">
         <v>19</v>
       </c>
       <c r="BB6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1716,13 @@
         <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
@@ -1670,19 +1737,19 @@
         <v>6</v>
       </c>
       <c r="AK7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL7" t="n">
         <v>14</v>
       </c>
       <c r="AM7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN7" t="n">
         <v>24</v>
       </c>
       <c r="AO7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP7" t="n">
         <v>29</v>
@@ -1691,7 +1758,7 @@
         <v>4</v>
       </c>
       <c r="AR7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
         <v>1</v>
@@ -1700,13 +1767,13 @@
         <v>1</v>
       </c>
       <c r="AU7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV7" t="n">
         <v>10</v>
       </c>
-      <c r="AV7" t="n">
-        <v>11</v>
-      </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
         <v>15</v>
@@ -1718,10 +1785,10 @@
         <v>3</v>
       </c>
       <c r="BA7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -1831,25 +1898,25 @@
         <v>3.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF8" t="n">
         <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH8" t="n">
         <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1858,10 +1925,10 @@
         <v>12</v>
       </c>
       <c r="AM8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,16 +1937,16 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS8" t="n">
         <v>13</v>
       </c>
       <c r="AT8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
         <v>3</v>
@@ -1900,13 +1967,13 @@
         <v>22</v>
       </c>
       <c r="BA8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB8" t="n">
         <v>5</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BC8" t="n">
         <v>6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>7</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -1935,58 +2002,58 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F9" t="n">
         <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>0.607</v>
+        <v>0.593</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J9" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L9" t="n">
         <v>5.3</v>
       </c>
       <c r="M9" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.366</v>
+        <v>0.373</v>
       </c>
       <c r="O9" t="n">
         <v>18</v>
       </c>
       <c r="P9" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R9" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="S9" t="n">
-        <v>29.8</v>
+        <v>29.5</v>
       </c>
       <c r="T9" t="n">
-        <v>40.3</v>
+        <v>39.8</v>
       </c>
       <c r="U9" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="V9" t="n">
         <v>12.9</v>
@@ -2001,22 +2068,22 @@
         <v>4.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>95.59999999999999</v>
+        <v>96</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AE9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF9" t="n">
         <v>8</v>
@@ -2025,55 +2092,55 @@
         <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AI9" t="n">
         <v>17</v>
       </c>
       <c r="AJ9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AL9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM9" t="n">
         <v>26</v>
       </c>
       <c r="AN9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO9" t="n">
         <v>21</v>
       </c>
       <c r="AP9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT9" t="n">
         <v>25</v>
       </c>
       <c r="AU9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY9" t="n">
         <v>5</v>
@@ -2088,7 +2155,7 @@
         <v>22</v>
       </c>
       <c r="BC9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-5.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>25</v>
@@ -2207,7 +2274,7 @@
         <v>25</v>
       </c>
       <c r="AH10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2222,10 +2289,10 @@
         <v>19</v>
       </c>
       <c r="AM10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO10" t="n">
         <v>2</v>
@@ -2243,7 +2310,7 @@
         <v>19</v>
       </c>
       <c r="AT10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU10" t="n">
         <v>24</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -2299,61 +2366,61 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F11" t="n">
         <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.645</v>
+        <v>0.633</v>
       </c>
       <c r="H11" t="n">
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="J11" t="n">
-        <v>79.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.441</v>
+        <v>0.443</v>
       </c>
       <c r="L11" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="M11" t="n">
-        <v>19.3</v>
+        <v>19</v>
       </c>
       <c r="N11" t="n">
-        <v>0.387</v>
+        <v>0.385</v>
       </c>
       <c r="O11" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="P11" t="n">
-        <v>25.5</v>
+        <v>25.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S11" t="n">
-        <v>32.6</v>
+        <v>32.3</v>
       </c>
       <c r="T11" t="n">
-        <v>43.2</v>
+        <v>42.8</v>
       </c>
       <c r="U11" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V11" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="W11" t="n">
         <v>6.5</v>
@@ -2368,16 +2435,16 @@
         <v>18.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.40000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC11" t="n">
         <v>3.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>5</v>
@@ -2389,43 +2456,43 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
         <v>28</v>
       </c>
       <c r="AJ11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AK11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
       </c>
       <c r="AM11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN11" t="n">
         <v>5</v>
       </c>
       <c r="AO11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ11" t="n">
         <v>2</v>
       </c>
       <c r="AR11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
         <v>21</v>
@@ -2440,7 +2507,7 @@
         <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ11" t="n">
         <v>4</v>
@@ -2452,7 +2519,7 @@
         <v>15</v>
       </c>
       <c r="BC11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
         <v>23</v>
@@ -2571,7 +2638,7 @@
         <v>23</v>
       </c>
       <c r="AH12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
         <v>2</v>
@@ -2580,7 +2647,7 @@
         <v>3</v>
       </c>
       <c r="AK12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL12" t="n">
         <v>13</v>
@@ -2592,7 +2659,7 @@
         <v>19</v>
       </c>
       <c r="AO12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP12" t="n">
         <v>28</v>
@@ -2601,10 +2668,10 @@
         <v>6</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AT12" t="n">
         <v>2</v>
@@ -2613,28 +2680,28 @@
         <v>4</v>
       </c>
       <c r="AV12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW12" t="n">
         <v>15</v>
       </c>
       <c r="AX12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
         <v>27</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2814,7 @@
         <v>26</v>
       </c>
       <c r="AF13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG13" t="n">
         <v>26</v>
@@ -2756,16 +2823,16 @@
         <v>1</v>
       </c>
       <c r="AI13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK13" t="n">
         <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM13" t="n">
         <v>19</v>
@@ -2786,16 +2853,16 @@
         <v>7</v>
       </c>
       <c r="AS13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU13" t="n">
         <v>19</v>
       </c>
       <c r="AV13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
         <v>13</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.821</v>
+        <v>0.828</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="J14" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K14" t="n">
         <v>0.472</v>
@@ -2872,31 +2939,31 @@
         <v>6.7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.37</v>
+        <v>0.376</v>
       </c>
       <c r="O14" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="P14" t="n">
-        <v>27.5</v>
+        <v>27.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R14" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S14" t="n">
-        <v>32.2</v>
+        <v>32.5</v>
       </c>
       <c r="T14" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="U14" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="V14" t="n">
         <v>14.1</v>
@@ -2905,28 +2972,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.9</v>
+        <v>106.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>3</v>
@@ -2947,28 +3014,28 @@
         <v>5</v>
       </c>
       <c r="AL14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM14" t="n">
         <v>15</v>
       </c>
-      <c r="AM14" t="n">
-        <v>13</v>
-      </c>
       <c r="AN14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AO14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP14" t="n">
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AT14" t="n">
         <v>3</v>
@@ -2977,19 +3044,19 @@
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW14" t="n">
         <v>2</v>
       </c>
       <c r="AX14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY14" t="n">
         <v>8</v>
       </c>
-      <c r="AY14" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -3027,25 +3094,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>0.333</v>
+        <v>0.345</v>
       </c>
       <c r="H15" t="n">
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
       <c r="I15" t="n">
-        <v>35.6</v>
+        <v>35.4</v>
       </c>
       <c r="J15" t="n">
-        <v>77.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>0.458</v>
@@ -3060,73 +3127,73 @@
         <v>0.336</v>
       </c>
       <c r="O15" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P15" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.751</v>
+        <v>0.753</v>
       </c>
       <c r="R15" t="n">
         <v>10</v>
       </c>
       <c r="S15" t="n">
-        <v>28.5</v>
+        <v>28.2</v>
       </c>
       <c r="T15" t="n">
-        <v>38.5</v>
+        <v>38.1</v>
       </c>
       <c r="U15" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="V15" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W15" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X15" t="n">
         <v>4.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z15" t="n">
         <v>21.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>94.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
         <v>23</v>
       </c>
       <c r="AF15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG15" t="n">
         <v>23</v>
       </c>
-      <c r="AG15" t="n">
-        <v>24</v>
-      </c>
       <c r="AH15" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ15" t="n">
         <v>26</v>
       </c>
       <c r="AK15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL15" t="n">
         <v>27</v>
@@ -3135,22 +3202,22 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>21</v>
       </c>
-      <c r="AO15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>22</v>
-      </c>
       <c r="AR15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AT15" t="n">
         <v>30</v>
@@ -3159,25 +3226,25 @@
         <v>30</v>
       </c>
       <c r="AV15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX15" t="n">
         <v>23</v>
       </c>
       <c r="AY15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC15" t="n">
         <v>24</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -3290,22 +3357,22 @@
         <v>22</v>
       </c>
       <c r="AE16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG16" t="n">
         <v>14</v>
       </c>
-      <c r="AF16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>13</v>
-      </c>
       <c r="AH16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
         <v>14</v>
       </c>
       <c r="AJ16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK16" t="n">
         <v>17</v>
@@ -3323,16 +3390,16 @@
         <v>28</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ16" t="n">
         <v>29</v>
       </c>
       <c r="AR16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT16" t="n">
         <v>22</v>
@@ -3341,7 +3408,7 @@
         <v>27</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW16" t="n">
         <v>6</v>
@@ -3353,13 +3420,13 @@
         <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BC16" t="n">
         <v>13</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -3406,73 +3473,73 @@
         <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>35.9</v>
+        <v>36.3</v>
       </c>
       <c r="J17" t="n">
         <v>82.8</v>
       </c>
       <c r="K17" t="n">
-        <v>0.433</v>
+        <v>0.439</v>
       </c>
       <c r="L17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
         <v>14.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.327</v>
+        <v>0.337</v>
       </c>
       <c r="O17" t="n">
-        <v>20.3</v>
+        <v>19.9</v>
       </c>
       <c r="P17" t="n">
-        <v>26.1</v>
+        <v>25.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.777</v>
+        <v>0.774</v>
       </c>
       <c r="R17" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S17" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="T17" t="n">
-        <v>44.1</v>
+        <v>43.7</v>
       </c>
       <c r="U17" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="V17" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="W17" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>96.90000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF17" t="n">
         <v>17</v>
@@ -3481,25 +3548,25 @@
         <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI17" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AJ17" t="n">
         <v>9</v>
       </c>
       <c r="AK17" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM17" t="n">
         <v>24</v>
       </c>
       <c r="AN17" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="n">
         <v>8</v>
@@ -3514,19 +3581,19 @@
         <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU17" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AV17" t="n">
         <v>21</v>
       </c>
       <c r="AW17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3538,10 +3605,10 @@
         <v>30</v>
       </c>
       <c r="BA17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BC17" t="n">
         <v>15</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E18" t="n">
         <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G18" t="n">
-        <v>0.172</v>
+        <v>0.179</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
@@ -3597,40 +3664,40 @@
         <v>0.429</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M18" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0.333</v>
+        <v>0.324</v>
       </c>
       <c r="O18" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P18" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.755</v>
+        <v>0.763</v>
       </c>
       <c r="R18" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S18" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T18" t="n">
         <v>41.1</v>
       </c>
       <c r="U18" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V18" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W18" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="X18" t="n">
         <v>4.3</v>
@@ -3639,31 +3706,31 @@
         <v>6.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB18" t="n">
-        <v>95.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7.5</v>
+        <v>-6.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
         <v>28</v>
       </c>
       <c r="AF18" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI18" t="n">
         <v>23</v>
@@ -3675,37 +3742,37 @@
         <v>29</v>
       </c>
       <c r="AL18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM18" t="n">
         <v>23</v>
       </c>
       <c r="AN18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO18" t="n">
         <v>12</v>
       </c>
       <c r="AP18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR18" t="n">
         <v>12</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>9</v>
-      </c>
       <c r="AS18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU18" t="n">
         <v>16</v>
       </c>
-      <c r="AU18" t="n">
-        <v>17</v>
-      </c>
       <c r="AV18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW18" t="n">
         <v>29</v>
@@ -3714,16 +3781,16 @@
         <v>25</v>
       </c>
       <c r="AY18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ18" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB18" t="n">
         <v>23</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>24</v>
       </c>
       <c r="BC18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -3755,55 +3822,55 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
         <v>15</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.483</v>
       </c>
       <c r="H19" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J19" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.444</v>
+        <v>0.442</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M19" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0.378</v>
+        <v>0.376</v>
       </c>
       <c r="O19" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="P19" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.79</v>
+        <v>0.788</v>
       </c>
       <c r="R19" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S19" t="n">
         <v>29.4</v>
       </c>
       <c r="T19" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U19" t="n">
         <v>18.7</v>
@@ -3812,7 +3879,7 @@
         <v>13.3</v>
       </c>
       <c r="W19" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="X19" t="n">
         <v>4.9</v>
@@ -3824,16 +3891,16 @@
         <v>23.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>100.9</v>
+        <v>100.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.1</v>
+        <v>-2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -3845,43 +3912,43 @@
         <v>16</v>
       </c>
       <c r="AH19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AI19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL19" t="n">
         <v>6</v>
       </c>
       <c r="AM19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO19" t="n">
         <v>4</v>
       </c>
       <c r="AP19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ19" t="n">
         <v>8</v>
       </c>
       <c r="AR19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS19" t="n">
         <v>22</v>
       </c>
       <c r="AT19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU19" t="n">
         <v>28</v>
@@ -3893,7 +3960,7 @@
         <v>25</v>
       </c>
       <c r="AX19" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
         <v>23</v>
@@ -3902,13 +3969,13 @@
         <v>29</v>
       </c>
       <c r="BA19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB19" t="n">
         <v>10</v>
       </c>
       <c r="BC19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4091,7 @@
         <v>5</v>
       </c>
       <c r="AG20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH20" t="n">
         <v>30</v>
@@ -4036,16 +4103,16 @@
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>7</v>
       </c>
       <c r="AM20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO20" t="n">
         <v>19</v>
@@ -4066,7 +4133,7 @@
         <v>26</v>
       </c>
       <c r="AU20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV20" t="n">
         <v>8</v>
@@ -4084,10 +4151,10 @@
         <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC20" t="n">
         <v>8</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -4203,13 +4270,13 @@
         <v>21</v>
       </c>
       <c r="AF21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG21" t="n">
         <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4218,7 +4285,7 @@
         <v>2</v>
       </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4230,7 +4297,7 @@
         <v>17</v>
       </c>
       <c r="AO21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP21" t="n">
         <v>27</v>
@@ -4239,7 +4306,7 @@
         <v>5</v>
       </c>
       <c r="AR21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
         <v>8</v>
@@ -4248,7 +4315,7 @@
         <v>9</v>
       </c>
       <c r="AU21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV21" t="n">
         <v>22</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E22" t="n">
         <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G22" t="n">
-        <v>0.097</v>
+        <v>0.1</v>
       </c>
       <c r="H22" t="n">
         <v>48</v>
@@ -4319,10 +4386,10 @@
         <v>35.6</v>
       </c>
       <c r="J22" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.435</v>
+        <v>0.433</v>
       </c>
       <c r="L22" t="n">
         <v>3.8</v>
@@ -4331,55 +4398,55 @@
         <v>10.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="O22" t="n">
         <v>17.8</v>
       </c>
       <c r="P22" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.746</v>
+        <v>0.743</v>
       </c>
       <c r="R22" t="n">
         <v>11.8</v>
       </c>
       <c r="S22" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T22" t="n">
         <v>42.1</v>
       </c>
       <c r="U22" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="V22" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="W22" t="n">
         <v>6.9</v>
       </c>
       <c r="X22" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Y22" t="n">
         <v>5.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>92.90000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="AC22" t="n">
         <v>-9.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
         <v>30</v>
@@ -4394,13 +4461,13 @@
         <v>26</v>
       </c>
       <c r="AI22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL22" t="n">
         <v>29</v>
@@ -4409,46 +4476,46 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ22" t="n">
         <v>25</v>
       </c>
       <c r="AR22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT22" t="n">
         <v>14</v>
       </c>
       <c r="AU22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV22" t="n">
         <v>24</v>
       </c>
       <c r="AW22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY22" t="n">
         <v>21</v>
       </c>
       <c r="AZ22" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB22" t="n">
         <v>29</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -4483,88 +4550,88 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F23" t="n">
         <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8</v>
+        <v>0.793</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="J23" t="n">
-        <v>78.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.459</v>
+        <v>0.456</v>
       </c>
       <c r="L23" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="M23" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.38</v>
+        <v>0.377</v>
       </c>
       <c r="O23" t="n">
         <v>19.1</v>
       </c>
       <c r="P23" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.712</v>
+        <v>0.709</v>
       </c>
       <c r="R23" t="n">
         <v>10</v>
       </c>
       <c r="S23" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T23" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U23" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="V23" t="n">
         <v>14.4</v>
       </c>
       <c r="W23" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X23" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Y23" t="n">
         <v>3.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA23" t="n">
         <v>22.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>101.2</v>
+        <v>100.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF23" t="n">
         <v>4</v>
@@ -4573,16 +4640,16 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AJ23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
         <v>2</v>
@@ -4591,19 +4658,19 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AS23" t="n">
         <v>3</v>
@@ -4618,7 +4685,7 @@
         <v>15</v>
       </c>
       <c r="AW23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX23" t="n">
         <v>3</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -4743,28 +4810,28 @@
         <v>-1.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ24" t="n">
         <v>12</v>
       </c>
       <c r="AK24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="n">
         <v>30</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP24" t="n">
         <v>14</v>
@@ -4785,13 +4852,13 @@
         <v>27</v>
       </c>
       <c r="AR24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU24" t="n">
         <v>20</v>
@@ -4809,7 +4876,7 @@
         <v>20</v>
       </c>
       <c r="AZ24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA24" t="n">
         <v>21</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -4928,16 +4995,16 @@
         <v>22</v>
       </c>
       <c r="AE25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG25" t="n">
         <v>14</v>
       </c>
-      <c r="AF25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>13</v>
-      </c>
       <c r="AH25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI25" t="n">
         <v>5</v>
@@ -4952,7 +5019,7 @@
         <v>9</v>
       </c>
       <c r="AM25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN25" t="n">
         <v>1</v>
@@ -4985,13 +5052,13 @@
         <v>27</v>
       </c>
       <c r="AX25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA25" t="n">
         <v>8</v>
@@ -5000,7 +5067,7 @@
         <v>4</v>
       </c>
       <c r="BC25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -5032,58 +5099,58 @@
         <v>30</v>
       </c>
       <c r="E26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G26" t="n">
-        <v>0.633</v>
+        <v>0.6</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.4</v>
       </c>
       <c r="J26" t="n">
-        <v>79.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.463</v>
+        <v>0.458</v>
       </c>
       <c r="L26" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M26" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.388</v>
+        <v>0.393</v>
       </c>
       <c r="O26" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="P26" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.78</v>
+        <v>0.775</v>
       </c>
       <c r="R26" t="n">
         <v>13.2</v>
       </c>
       <c r="S26" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="T26" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U26" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V26" t="n">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
       <c r="W26" t="n">
         <v>6.9</v>
@@ -5092,97 +5159,97 @@
         <v>5.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="n">
         <v>20.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH26" t="n">
         <v>7</v>
       </c>
-      <c r="AF26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG26" t="n">
+      <c r="AI26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK26" t="n">
         <v>9</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>7</v>
       </c>
       <c r="AL26" t="n">
         <v>5</v>
       </c>
       <c r="AM26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS26" t="n">
         <v>30</v>
       </c>
       <c r="AT26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>14</v>
       </c>
-      <c r="AV26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>15</v>
-      </c>
       <c r="BA26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
@@ -5301,16 +5368,16 @@
         <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AI27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK27" t="n">
         <v>12</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>13</v>
       </c>
       <c r="AL27" t="n">
         <v>21</v>
@@ -5319,19 +5386,19 @@
         <v>18</v>
       </c>
       <c r="AN27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO27" t="n">
         <v>20</v>
       </c>
       <c r="AP27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ27" t="n">
         <v>9</v>
       </c>
       <c r="AR27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS27" t="n">
         <v>26</v>
@@ -5346,19 +5413,19 @@
         <v>23</v>
       </c>
       <c r="AW27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ27" t="n">
         <v>28</v>
       </c>
       <c r="BA27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB27" t="n">
         <v>17</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -5393,25 +5460,25 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F28" t="n">
         <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>0.667</v>
+        <v>0.655</v>
       </c>
       <c r="H28" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="I28" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J28" t="n">
-        <v>79.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="K28" t="n">
         <v>0.463</v>
@@ -5420,58 +5487,58 @@
         <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.397</v>
+        <v>0.399</v>
       </c>
       <c r="O28" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="P28" t="n">
         <v>20</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.753</v>
+        <v>0.751</v>
       </c>
       <c r="R28" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S28" t="n">
         <v>32.2</v>
       </c>
       <c r="T28" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U28" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V28" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="W28" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="X28" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AB28" t="n">
-        <v>96.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC28" t="n">
         <v>3.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5483,16 +5550,16 @@
         <v>5</v>
       </c>
       <c r="AH28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ28" t="n">
         <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
         <v>4</v>
@@ -5510,10 +5577,10 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AR28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS28" t="n">
         <v>7</v>
@@ -5522,7 +5589,7 @@
         <v>21</v>
       </c>
       <c r="AU28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV28" t="n">
         <v>1</v>
@@ -5534,7 +5601,7 @@
         <v>27</v>
       </c>
       <c r="AY28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E29" t="n">
         <v>12</v>
       </c>
       <c r="F29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4</v>
+        <v>0.414</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
@@ -5593,7 +5660,7 @@
         <v>35.2</v>
       </c>
       <c r="J29" t="n">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="K29" t="n">
         <v>0.448</v>
@@ -5605,28 +5672,28 @@
         <v>16.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0.376</v>
+        <v>0.377</v>
       </c>
       <c r="O29" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="P29" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.832</v>
+        <v>0.829</v>
       </c>
       <c r="R29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="T29" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="U29" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="V29" t="n">
         <v>13.4</v>
@@ -5635,40 +5702,40 @@
         <v>6.3</v>
       </c>
       <c r="X29" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z29" t="n">
         <v>18.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>95.90000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.6</v>
+        <v>-3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH29" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AI29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ29" t="n">
         <v>23</v>
@@ -5677,31 +5744,31 @@
         <v>18</v>
       </c>
       <c r="AL29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM29" t="n">
         <v>20</v>
       </c>
       <c r="AN29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AO29" t="n">
         <v>10</v>
       </c>
       <c r="AP29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
       </c>
       <c r="AR29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AT29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU29" t="n">
         <v>7</v>
@@ -5713,16 +5780,16 @@
         <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ29" t="n">
         <v>2</v>
       </c>
       <c r="BA29" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BB29" t="n">
         <v>21</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -5757,25 +5824,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E30" t="n">
         <v>18</v>
       </c>
       <c r="F30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.581</v>
       </c>
       <c r="H30" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="I30" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
       <c r="J30" t="n">
-        <v>79.5</v>
+        <v>78.8</v>
       </c>
       <c r="K30" t="n">
         <v>0.473</v>
@@ -5787,19 +5854,19 @@
         <v>12.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0.335</v>
+        <v>0.333</v>
       </c>
       <c r="O30" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="P30" t="n">
-        <v>26.9</v>
+        <v>27.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="R30" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S30" t="n">
         <v>29.5</v>
@@ -5808,52 +5875,52 @@
         <v>41.6</v>
       </c>
       <c r="U30" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="V30" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="W30" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X30" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y30" t="n">
         <v>5.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>100.2</v>
+        <v>99.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF30" t="n">
         <v>15</v>
       </c>
       <c r="AG30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH30" t="n">
         <v>15</v>
       </c>
-      <c r="AH30" t="n">
-        <v>4</v>
-      </c>
       <c r="AI30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ30" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AK30" t="n">
         <v>4</v>
@@ -5865,22 +5932,22 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AP30" t="n">
         <v>5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
         <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT30" t="n">
         <v>15</v>
@@ -5901,16 +5968,16 @@
         <v>18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA30" t="n">
         <v>3</v>
       </c>
       <c r="BB30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
@@ -5939,103 +6006,103 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
         <v>23</v>
       </c>
       <c r="G31" t="n">
-        <v>0.179</v>
+        <v>0.148</v>
       </c>
       <c r="H31" t="n">
         <v>48.2</v>
       </c>
       <c r="I31" t="n">
-        <v>36.3</v>
+        <v>36</v>
       </c>
       <c r="J31" t="n">
-        <v>82.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K31" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L31" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M31" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0.319</v>
+        <v>0.322</v>
       </c>
       <c r="O31" t="n">
-        <v>17.3</v>
+        <v>17.6</v>
       </c>
       <c r="P31" t="n">
-        <v>23</v>
+        <v>23.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.753</v>
+        <v>0.755</v>
       </c>
       <c r="R31" t="n">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="S31" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="T31" t="n">
-        <v>40.3</v>
+        <v>40.1</v>
       </c>
       <c r="U31" t="n">
-        <v>20.7</v>
+        <v>20.3</v>
       </c>
       <c r="V31" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W31" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="X31" t="n">
         <v>4.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>95.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>-6.3</v>
+        <v>-6.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AE31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF31" t="n">
         <v>27</v>
       </c>
       <c r="AG31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI31" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK31" t="n">
         <v>24</v>
@@ -6047,40 +6114,40 @@
         <v>16</v>
       </c>
       <c r="AN31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS31" t="n">
         <v>27</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>24</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>28</v>
       </c>
       <c r="AT31" t="n">
         <v>24</v>
       </c>
       <c r="AU31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX31" t="n">
         <v>26</v>
       </c>
       <c r="AY31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ31" t="n">
         <v>16</v>
@@ -6089,7 +6156,7 @@
         <v>28</v>
       </c>
       <c r="BB31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC31" t="n">
         <v>27</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-27-2008-09</t>
+          <t>2008-12-27</t>
         </is>
       </c>
     </row>
